--- a/output/pdf_financials_xlsx/CUAU.xlsx
+++ b/output/pdf_financials_xlsx/CUAU.xlsx
@@ -1978,13 +1978,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.388926</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.543801</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>2.310131</v>
       </c>
     </row>
     <row r="93">
@@ -3135,7 +3135,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>0.388926</v>
       </c>

--- a/output/pdf_financials_xlsx/CUAU.xlsx
+++ b/output/pdf_financials_xlsx/CUAU.xlsx
@@ -594,10 +594,10 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.127247</v>
+        <v>1.514523</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.109254</v>
+        <v>4.926196</v>
       </c>
     </row>
     <row r="11">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.127247</v>
+        <v>-1.514523</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.109254</v>
+        <v>-4.926196</v>
       </c>
     </row>
     <row r="12">
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.019073</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.109254</v>
       </c>
     </row>
     <row r="13">
@@ -908,10 +908,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.64177</v>
+        <v>-1.660843</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-4.816942</v>
+        <v>-4.926196</v>
       </c>
     </row>
     <row r="28">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.64177</v>
+        <v>-1.660843</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-4.816942</v>
+        <v>-4.926196</v>
       </c>
     </row>
     <row r="30">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.154062</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.124439</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>13.298621</v>
       </c>
     </row>
     <row r="35">
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.154062</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.124439</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>13.298621</v>
       </c>
     </row>
     <row r="37">
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.25534</v>
+        <v>0.101278</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.165123</v>
+        <v>0.040684</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>13.391564</v>
+        <v>0.092943</v>
       </c>
     </row>
     <row r="49">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5417,7 +5417,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-1.514523</v>
+        <v>1.514523</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>-4.926196</v>
+        <v>4.926196</v>
       </c>
     </row>
     <row r="85">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">

--- a/output/pdf_financials_xlsx/CUAU.xlsx
+++ b/output/pdf_financials_xlsx/CUAU.xlsx
@@ -480,10 +480,8 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0</v>
@@ -498,10 +496,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -516,10 +512,8 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C6" s="3" t="n">
         <v>0</v>
@@ -534,16 +528,14 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.390495</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.375569</v>
+        <v>0.439569</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.623765</v>
+        <v>0.688711</v>
       </c>
     </row>
     <row r="8">
@@ -552,10 +544,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>0</v>
@@ -570,10 +560,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0.163662</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.182653</v>
@@ -588,10 +576,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>1.165863</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>1.514523</v>
@@ -606,10 +592,8 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-1.165863</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>-1.514523</v>
@@ -624,10 +608,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0.019161</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.019073</v>
@@ -642,10 +624,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -660,10 +640,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -678,10 +656,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>0</v>
@@ -696,10 +672,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-1.146702</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-1.64177</v>
@@ -714,10 +688,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -776,10 +748,8 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-1.146702</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>-1.64177</v>
@@ -794,10 +764,8 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
         <v>0</v>
@@ -812,10 +780,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -830,10 +796,8 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>-1.146702</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>-1.64177</v>
@@ -848,10 +812,8 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>-0.04</v>
@@ -866,10 +828,8 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.03</v>
       </c>
       <c r="C25" s="3" t="n">
         <v>-0.04</v>
@@ -884,10 +844,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>38.2234</v>
       </c>
       <c r="C26" s="3" t="n">
         <v>41.04425</v>
@@ -902,10 +860,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-1.165863</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-1.660843</v>
@@ -920,10 +876,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -938,10 +892,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-1.165863</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-1.660843</v>
@@ -978,10 +930,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -2080,10 +2030,8 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-1.146702</v>
       </c>
       <c r="C99" s="3" t="n">
         <v>-1.64177</v>
@@ -2098,10 +2046,8 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C100" s="3" t="n">
         <v>0</v>
@@ -2116,10 +2062,8 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>-0.000362</v>
       </c>
       <c r="C101" s="3" t="n">
         <v>-0.011452</v>
@@ -2134,10 +2078,8 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C102" s="3" t="n">
         <v>0</v>
@@ -2152,10 +2094,8 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.055077</v>
       </c>
       <c r="C103" s="3" t="n">
         <v>0.026734</v>
@@ -2170,10 +2110,8 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.013248</v>
       </c>
       <c r="C104" s="3" t="n">
         <v>0.196107</v>
@@ -2188,10 +2126,8 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C105" s="3" t="n">
         <v>0</v>
@@ -2206,10 +2142,8 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.068687</v>
       </c>
       <c r="C106" s="3" t="n">
         <v>0.211389</v>
@@ -2224,10 +2158,8 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.230429</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>2.490184</v>
@@ -2242,10 +2174,8 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C108" s="3" t="n">
         <v>0</v>
@@ -2260,10 +2190,8 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C109" s="3" t="n">
         <v>0</v>
@@ -2278,10 +2206,8 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
         <v>0</v>
@@ -2296,10 +2222,8 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2314,10 +2238,8 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
         <v>0</v>
@@ -2332,10 +2254,8 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C113" s="3" t="n">
         <v>0</v>
@@ -2350,10 +2270,8 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C114" s="3" t="n">
         <v>0</v>
@@ -2368,10 +2286,8 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
         <v>0</v>
@@ -2386,10 +2302,8 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C116" s="3" t="n">
         <v>0</v>
@@ -2404,10 +2318,8 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C117" s="3" t="n">
         <v>0</v>
@@ -2422,10 +2334,8 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C118" s="3" t="n">
         <v>0</v>
@@ -2440,10 +2350,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="3" t="n">
         <v>-0.036447</v>
@@ -2458,10 +2366,8 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C120" s="3" t="n">
         <v>0</v>
@@ -2476,10 +2382,8 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C121" s="3" t="n">
         <v>0</v>
@@ -2494,10 +2398,8 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C122" s="3" t="n">
         <v>0</v>
@@ -2512,10 +2414,8 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C123" s="3" t="n">
         <v>0</v>
@@ -2530,10 +2430,8 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
         <v>0</v>
@@ -2548,10 +2446,8 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
         <v>0</v>
@@ -2566,10 +2462,8 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C126" s="3" t="n">
         <v>0</v>
@@ -2606,10 +2500,8 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C128" s="3" t="n">
         <v>-0.102483</v>
@@ -2624,10 +2516,8 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0.031836</v>
       </c>
       <c r="C129" s="3" t="n">
         <v>2.075617</v>
@@ -2642,10 +2532,8 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>1.346218</v>
       </c>
       <c r="C130" s="3" t="n">
         <v>0.154062</v>
@@ -2660,10 +2548,8 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>-0.013372</v>
       </c>
       <c r="C131" s="3" t="n">
         <v>0.003774</v>
@@ -2678,10 +2564,8 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-1.192156</v>
       </c>
       <c r="C132" s="3" t="n">
         <v>0.970377</v>
@@ -2696,10 +2580,8 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.154062</v>
       </c>
       <c r="C133" s="3" t="n">
         <v>1.124439</v>
@@ -2714,10 +2596,8 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2732,10 +2612,8 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-1.21062</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-1.072567</v>
@@ -2755,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3454,10 +3332,8 @@
           <t>NetIncomeFromContinuingOperations</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="5" t="n">
+        <v>-1.146702</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>-1.64177</v>
@@ -3551,10 +3427,8 @@
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="5" t="n">
+        <v>-0.000374</v>
       </c>
       <c r="F25" s="5" t="n">
         <v>0.000875</v>
@@ -3615,10 +3489,8 @@
           <t>ChangeInReceivables</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="5" t="n">
+        <v>-0.000362</v>
       </c>
       <c r="F27" s="5" t="n">
         <v>-0.011452</v>
@@ -3648,10 +3520,8 @@
           <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="5" t="n">
+        <v>-0.013248</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.176297</v>
@@ -3681,10 +3551,8 @@
           <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E29" s="5" t="n">
+        <v>-0.055077</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0.026734</v>
@@ -3714,10 +3582,8 @@
           <t>OperatingCashFlow</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E30" s="5" t="n">
+        <v>-1.21062</v>
       </c>
       <c r="F30" s="5" t="n">
         <v>-1.072567</v>
@@ -3808,7 +3674,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -3939,10 +3809,8 @@
           <t>FinancingCashFlow</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="5" t="n">
+        <v>0.031836</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>2.075617</v>
@@ -3972,10 +3840,8 @@
           <t>EffectOfExchangeRateChanges</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="5" t="n">
+        <v>-0.013372</v>
       </c>
       <c r="F38" s="5" t="n">
         <v>0.003774</v>
@@ -4005,10 +3871,8 @@
           <t>ChangesInCash</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" s="5" t="n">
+        <v>-1.192156</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>0.970377</v>
@@ -4038,10 +3902,8 @@
           <t>BeginningCashPosition</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E40" s="5" t="n">
+        <v>1.346218</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0.154062</v>
@@ -4071,10 +3933,8 @@
           <t>EndCashPosition</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E41" s="5" t="n">
+        <v>0.154062</v>
       </c>
       <c r="F41" s="5" t="n">
         <v>1.124439</v>
@@ -4100,10 +3960,8 @@
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E42" s="5" t="n">
+        <v>0.046201</v>
       </c>
       <c r="F42" s="5" t="n">
         <v>0.116691</v>
@@ -4925,50 +4783,48 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not involving the use of cash</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Consulting (Note 6) $</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>0.0435</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>0.090159</v>
+          <t>Interest write-off</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" s="5" t="n">
+        <v>0.005143</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Corporate development</t>
+          <t>Mineral property acquisition costs</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
@@ -4978,517 +4834,501 @@
         </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.053092</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>0.068546</v>
+        <v>-0.036447</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Directors’ fees (Note 6)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Net cash provided by investing activities</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F71" s="5" t="n">
-        <v>0.064</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>0.064946</v>
+        <v>-0.036447</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenditures (Notes 4 and 6)</t>
+          <t>Interest received on note repayment</t>
         </is>
       </c>
       <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>0.480468</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>1.410562</v>
+      <c r="E72" s="5" t="n">
+        <v>0.001836</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>0.00207</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>0.381268</v>
+          <t>Repayment of notes receivable</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Investor relations (Note 6)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>0.127247</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>0.172452</v>
+          <t>Reclassification on expiry of warrants $</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.108502</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Non-cash investing and financing activities</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Listing expenses</t>
+          <t>Shares returned to treasury on expiry of notes receivable $</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0.034513</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>0.035577</v>
+      <c r="E75" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number         Amount            Loss            Reserves             Deficit            Equity</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Management fees (Note 6)</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance, December 31, 2022 36,761,919 $ 6,608,564 $ (15,222) $ 543,629 $</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>2.413134</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>0.2025</v>
+        <v>-4.723837</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Number         Amount            Loss            Reserves             Deficit            Equity</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Marketing (Note 6)</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>0.139153</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.092767</v>
+          <t>Shares returned to treasury (750,000) (90,000) - -</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" s="5" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Reclassification on expiry of stock</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Office and administration (Note 6)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Reclassification on expiry of stock options - - - (46,201)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F78" s="5" t="n">
-        <v>0.052617</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>0.08073</v>
+        <v>0.046201</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Reclassification on expiry of broker</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Reclassification on expiry of broker warrants - - - (108,502)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.091729</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>0.10737</v>
+        <v>0.108502</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Reclassification on expiry of broker</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salaries and wages</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>SalariesAndWages</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.02191</v>
+          <t>Comprehensive loss for the year - - (13,750) -</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" s="5" t="n">
+        <v>-1.160452</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>-1.146702</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Reclassification on expiry of broker</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Share-based payments (Notes 5 and 6)</t>
+          <t>Balance, December 31, 2023 36,011,919 6,518,564 (28,972) 388,926</t>
         </is>
       </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E81" s="5" t="n">
+        <v>1.162682</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>0.230429</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>2.029326</v>
+        <v>-5.715836</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Reclassification on expiry of broker</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Transfer agent and filing fees</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>0.035189</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>0.014081</v>
+          <t>Private placement 8,953,000 1,790,600 - -</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
+        <v>1.7906</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Reclassification on expiry of broker</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.025516</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>0.154002</v>
+          <t>Share issuance costs - (143,620) - 41,137</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" s="5" t="n">
+        <v>-0.102483</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Reclassification on expiry of broker</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Total expenses</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>1.514523</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>4.926196</v>
+          <t>Shares issued on exercise of warrants 1,937,500 387,500 - -</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" s="5" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Reclassification on expiry of broker</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0.019073</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>0.109254</v>
+          <t>Shares issued for debt 283,000 76,410 - -</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" s="5" t="n">
+        <v>0.07641000000000001</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Reclassification on expiry of broker</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Loss on settlement of accounts payable (Note 5)</t>
+          <t>Shares issued for mineral property 3,000,000 750,000 - -</t>
         </is>
       </c>
       <c r="D86" t="inlineStr"/>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>-0.01981</v>
+      <c r="E86" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -5499,17 +5339,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Reclassification on expiry of stock</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Write-off of mineral properties (Note 4)</t>
+          <t>Reclassification on expiry of stock options - - - (116,691)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr"/>
@@ -5519,7 +5359,7 @@
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.12651</v>
+        <v>0.116691</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -5530,96 +5370,94 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Reclassification on expiry of stock</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Other income (expenses) total</t>
+          <t>Share-based payments - - - 230,429</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>0.127247</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>0.109254</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="n">
+        <v>0.230429</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Other income (expenses)</t>
+          <t>Reclassification on expiry of stock</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Net loss</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Comprehensive loss for the year - - 5,580 -</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" s="5" t="n">
+        <v>-1.63619</v>
       </c>
       <c r="F89" s="5" t="n">
         <v>-1.64177</v>
       </c>
-      <c r="G89" s="5" t="n">
-        <v>-4.816942</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>Reclassification on expiry of stock</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Foreign exchange on translation</t>
+          <t>Balance, December 31, 2024 50,185,419 $ 9,379,454 $ (23,392) $ 543,801 $</t>
         </is>
       </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E90" s="5" t="n">
+        <v>2.658948</v>
       </c>
       <c r="F90" s="5" t="n">
-        <v>0.00558</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>-0.051295</v>
+        <v>-7.240915</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
@@ -5630,17 +5468,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Comprehensive loss for the year $</t>
+          <t>Consulting (Note 6) $</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5649,10 +5487,10 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>-1.63619</v>
+        <v>0.0435</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-4.868237</v>
+        <v>0.090159</v>
       </c>
     </row>
     <row r="92">
@@ -5663,29 +5501,23 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Other comprehensive loss</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Corporate development</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>0.045785</v>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-4e-08</v>
+        <v>0.053092</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-9e-08</v>
+        <v>0.068546</v>
       </c>
     </row>
     <row r="93">
@@ -5696,25 +5528,1062 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Directors’ fees (Note 6)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.064946</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures (Notes 4 and 6)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>0.480468</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>1.410562</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="n">
+        <v>-0.004612</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>0.00207</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.381268</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Investor relations (Note 6)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>0.127247</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.172452</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Listing expenses</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" s="5" t="n">
+        <v>0.031063</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>0.034513</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.035577</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Management fees (Note 6)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F98" s="5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.2025</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Marketing (Note 6)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F99" s="5" t="n">
+        <v>0.139153</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.092767</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Office and administration (Note 6)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F100" s="5" t="n">
+        <v>0.052617</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.08073</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E101" s="5" t="n">
+        <v>0.117632</v>
+      </c>
+      <c r="F101" s="5" t="n">
+        <v>0.091729</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.10737</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Salaries and wages</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>SalariesAndWages</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.02191</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Share-based payments (Notes 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="n">
+        <v>0.230429</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>2.029326</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Transfer agent and filing fees</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E104" s="5" t="n">
+        <v>0.034605</v>
+      </c>
+      <c r="F104" s="5" t="n">
+        <v>0.035189</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.014081</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="n">
+        <v>0.019332</v>
+      </c>
+      <c r="F105" s="5" t="n">
+        <v>0.025516</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.154002</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Total expenses</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>1.165863</v>
+      </c>
+      <c r="F106" s="5" t="n">
+        <v>1.514523</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>4.926196</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F107" s="5" t="n">
+        <v>0.019073</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.109254</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Loss on settlement of accounts payable (Note 5)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F108" s="5" t="n">
+        <v>-0.01981</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Write-off of mineral properties (Note 4)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F109" s="5" t="n">
+        <v>-0.12651</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Other income (expenses) total</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>0.019161</v>
+      </c>
+      <c r="F110" s="5" t="n">
+        <v>0.127247</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.109254</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Net loss</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="n">
+        <v>-1.146702</v>
+      </c>
+      <c r="F111" s="5" t="n">
+        <v>-1.64177</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>-4.816942</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Foreign exchange on translation</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" s="5" t="n">
+        <v>-0.01375</v>
+      </c>
+      <c r="F112" s="5" t="n">
+        <v>0.00558</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>-0.051295</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>-1.160452</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>-1.63619</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>-4.868237</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="n">
+        <v>-3e-08</v>
+      </c>
+      <c r="F114" s="5" t="n">
+        <v>-4e-08</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>-9e-08</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding basic and diluted</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" s="5" t="n">
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" s="5" t="n">
+        <v>36.420823</v>
+      </c>
+      <c r="F115" s="5" t="n">
         <v>42.406322</v>
       </c>
-      <c r="G93" s="5" t="n">
+      <c r="G115" s="5" t="n">
         <v>54.555103</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Consulting (Note 7) $</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="F116" s="5" t="n">
+        <v>0.0435</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Directors’ fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="F117" s="5" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation expenditures (Notes 5 and 7)</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" s="5" t="n">
+        <v>0.421838</v>
+      </c>
+      <c r="F118" s="5" t="n">
+        <v>0.480468</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Investor relations (Note 7)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="n">
+        <v>0.08058700000000001</v>
+      </c>
+      <c r="F119" s="5" t="n">
+        <v>0.127247</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Management fees (Note 7)</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="F120" s="5" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Marketing (Note 7)</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="n">
+        <v>0.121662</v>
+      </c>
+      <c r="F121" s="5" t="n">
+        <v>0.139153</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Office and administration (Note 7)</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="n">
+        <v>0.056971</v>
+      </c>
+      <c r="F122" s="5" t="n">
+        <v>0.052617</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Share-based payments (Notes 7 and 8)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="n">
+        <v>0.230429</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Interest income (Note 4)</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="n">
+        <v>0.019161</v>
+      </c>
+      <c r="F124" s="5" t="n">
+        <v>0.019073</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Loss on settlement of accounts payable (Note 6)</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="n">
+        <v>-0.01981</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Other income (expenses)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Write-off of mineral properties (Note 5)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="n">
+        <v>-0.12651</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
   </sheetData>
